--- a/data/authored_preview/C_vat/B1_C002_c185935c/inputs/05_대표_카드지출.xlsx
+++ b/data/authored_preview/C_vat/B1_C002_c185935c/inputs/05_대표_카드지출.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>거래 증빙 / 5번 / activity_id</t>
+          <t>거래 증빙 / 5번 / 수령 및 사용 활동 번호</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>거래 증빙 / 6번 / activity_id</t>
+          <t>거래 증빙 / 6번 / 수령 및 사용 활동 번호</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
